--- a/Borsdata - Export/APRTEC-APR Technologies.xlsx
+++ b/Borsdata - Export/APRTEC-APR Technologies.xlsx
@@ -195,364 +195,370 @@
     <x:t>ISIN</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-07-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rullande 12 månader</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3 år</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Börsdata ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Industri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quarter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kvartal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sektor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elektroniska komponenter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bransch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spotlight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nyckeltal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lista</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sverige</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Land</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Instrument</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q1 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senaste rapport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senaste aktiekurs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kursdatum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PriceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daglig aktiekurshistorik</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;20 år</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekursvaluta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PriceWeek</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veckovis kurshistorik</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rapportvaluta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PriceMonth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Månadsvis kurshistorik</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Report</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoomsättning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bruttoresultat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rörelseresultat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resultat Före Skatt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resultat Hänföring Aktieägare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vinst/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antal Aktier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Utdelning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Immateriella tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Materiella tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Finansiella tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Anläggningstillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassa/Bank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Omsättningstillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Eget Kapital</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Långfristiga Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kortfristiga Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Eget Kapital och Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoskuld</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassaf LöpandeVerk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassaf Investeringsverk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassaf Finansieringsverk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Åretskassaflöde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FrittKassaflöde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBITDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Totala Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Totala Skulder och Eget kapital</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoomsättning/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBITDA / Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eget Kapital/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoskuld/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Operativ kassaflöde/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FCF / Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Årets kassaflöde/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBITDA-marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bruttomarginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rörelsemarginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vinstmarginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Immat.tillgång.-%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassa-%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rörelsekapital-%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Soliditet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avkastning På EK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avkastning på T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OP-marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Capex %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FCF-marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Utdelning/FCF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Årets kassaflöde marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs Snitt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs Högsta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs Lägsta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direktavkastning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/EBIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/EBITDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/FCF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/OP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E/EV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBIT/EV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/(E)x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/B-tang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Openprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Highprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lowprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closeprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Volume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Highligted header</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Header</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Common value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Highlighted value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-14</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-07-09</x:t>
   </x:si>
   <x:si>
-    <x:t>R12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rullande 12 månader</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3 år</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Börsdata ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Industri</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quarter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kvartal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sektor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elektroniska komponenter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bransch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Spotlight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nyckeltal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lista</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sverige</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Land</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Instrument</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q1 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senaste rapport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senaste aktiekurs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kursdatum</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-07-08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PriceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Daglig aktiekurshistorik</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;20 år</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekursvaluta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PriceWeek</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veckovis kurshistorik</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rapportvaluta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PriceMonth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Månadsvis kurshistorik</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Report</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoomsättning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bruttoresultat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rörelseresultat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resultat Före Skatt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resultat Hänföring Aktieägare</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vinst/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Antal Aktier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Utdelning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Immateriella tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Materiella tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Finansiella tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Anläggningstillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassa/Bank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Omsättningstillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Eget Kapital</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Långfristiga Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kortfristiga Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Eget Kapital och Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoskuld</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassaf LöpandeVerk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassaf Investeringsverk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassaf Finansieringsverk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Åretskassaflöde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FrittKassaflöde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBITDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Totala Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Totala Skulder och Eget kapital</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoomsättning/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBITDA / Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Eget Kapital/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoskuld/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Operativ kassaflöde/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FCF / Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Årets kassaflöde/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBITDA-marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bruttomarginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rörelsemarginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vinstmarginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Immat.tillgång.-%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassa-%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rörelsekapital-%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Soliditet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Avkastning På EK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Avkastning på T</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OP-marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Capex %</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FCF-marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Utdelning/FCF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Årets kassaflöde marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs Snitt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs Högsta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs Lägsta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Direktavkastning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/EBIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/EBITDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/FCF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/OP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E/EV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBIT/EV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/(E)x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/B-tang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Openprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Highprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lowprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closeprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Volume</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Highligted header</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Header</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Common value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Highlighted value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-07-10</x:t>
   </x:si>
   <x:si>
     <x:t>2026-07-07</x:t>
@@ -4086,7 +4092,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C25" s="107">
-        <x:v>21.5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D25" s="79"/>
       <x:c r="E25" s="102" t="s">
@@ -6060,7 +6066,7 @@
         <x:v>-18.3859996795654</x:v>
       </x:c>
       <x:c r="L65" s="141">
-        <x:v>-23.7280006408691</x:v>
+        <x:v>-30.9020004272461</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6084,7 +6090,7 @@
         <x:v>16.1609992980957</x:v>
       </x:c>
       <x:c r="L66" s="141">
-        <x:v>28.1690006256104</x:v>
+        <x:v>36.6860008239746</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6108,7 +6114,7 @@
         <x:v>2.80399990081787</x:v>
       </x:c>
       <x:c r="L67" s="141">
-        <x:v>5.08699989318848</x:v>
+        <x:v>6.625</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6152,7 +6158,7 @@
         <x:v>-13.7819995880127</x:v>
       </x:c>
       <x:c r="L69" s="141">
-        <x:v>-18.9200000762939</x:v>
+        <x:v>-25.7189998626709</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6174,7 +6180,7 @@
         <x:v>-31.0650005340576</x:v>
       </x:c>
       <x:c r="L70" s="141">
-        <x:v>-29.6690006256104</x:v>
+        <x:v>-40.3310012817383</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6196,7 +6202,7 @@
         <x:v>-13.0620002746582</x:v>
       </x:c>
       <x:c r="L71" s="141">
-        <x:v>-18.4839992523193</x:v>
+        <x:v>-25.1259994506836</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6218,7 +6224,7 @@
         <x:v>-12.1079998016357</x:v>
       </x:c>
       <x:c r="L72" s="141">
-        <x:v>-19.9360008239746</x:v>
+        <x:v>-27.1009998321533</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6242,7 +6248,7 @@
         <x:v>-19.2770004272461</x:v>
       </x:c>
       <x:c r="L73" s="141">
-        <x:v>-28.7530002593994</x:v>
+        <x:v>-39.0859985351562</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6264,7 +6270,7 @@
         <x:v>11.4820003509521</x:v>
       </x:c>
       <x:c r="L74" s="141">
-        <x:v>23.6989994049072</x:v>
+        <x:v>32.2150001525879</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6286,7 +6292,7 @@
         <x:v>-7.6560001373291</x:v>
       </x:c>
       <x:c r="L75" s="141">
-        <x:v>-5.40999984741211</x:v>
+        <x:v>-3.98000001907349</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6308,7 +6314,7 @@
         <x:v>-7.25600004196167</x:v>
       </x:c>
       <x:c r="L76" s="141">
-        <x:v>-5.28499984741211</x:v>
+        <x:v>-3.88800001144409</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6328,7 +6334,7 @@
       <x:c r="J77" s="139"/>
       <x:c r="K77" s="139"/>
       <x:c r="L77" s="141">
-        <x:v>-31.923999786377</x:v>
+        <x:v>-41.576000213623</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6352,7 +6358,7 @@
         <x:v>3.5239999294281</x:v>
       </x:c>
       <x:c r="L78" s="141">
-        <x:v>6.33599996566772</x:v>
+        <x:v>8.2519998550415</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:16075" x14ac:dyDescent="0.25">
@@ -8439,19 +8445,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="150">
-        <x:v>21.3</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="C2" s="150">
-        <x:v>22.4</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="D2" s="150">
-        <x:v>20.5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E2" s="151">
-        <x:v>21.5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F2" s="152">
-        <x:v>48398</x:v>
+        <x:v>55854</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -8459,19 +8465,19 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="150">
-        <x:v>23.3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C3" s="150">
-        <x:v>24.5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D3" s="150">
-        <x:v>20</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="E3" s="151">
-        <x:v>20.5</x:v>
+        <x:v>24.3</x:v>
       </x:c>
       <x:c r="F3" s="152">
-        <x:v>63262</x:v>
+        <x:v>39688</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -8479,19 +8485,19 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B4" s="150">
-        <x:v>25.1</x:v>
+        <x:v>21.3</x:v>
       </x:c>
       <x:c r="C4" s="150">
-        <x:v>26</x:v>
+        <x:v>22.4</x:v>
       </x:c>
       <x:c r="D4" s="150">
-        <x:v>23</x:v>
+        <x:v>20.5</x:v>
       </x:c>
       <x:c r="E4" s="151">
-        <x:v>23</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="F4" s="152">
-        <x:v>32237</x:v>
+        <x:v>48398</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -8499,19 +8505,19 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B5" s="150">
-        <x:v>25.6</x:v>
+        <x:v>23.3</x:v>
       </x:c>
       <x:c r="C5" s="150">
-        <x:v>27.1</x:v>
+        <x:v>24.5</x:v>
       </x:c>
       <x:c r="D5" s="150">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="151">
-        <x:v>26.3</x:v>
+        <x:v>20.5</x:v>
       </x:c>
       <x:c r="F5" s="152">
-        <x:v>18965</x:v>
+        <x:v>63262</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -8519,19 +8525,19 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B6" s="150">
-        <x:v>25.7</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C6" s="150">
-        <x:v>27.1</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="150">
-        <x:v>24.1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="151">
-        <x:v>25.6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="152">
-        <x:v>17332</x:v>
+        <x:v>32237</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -8539,19 +8545,19 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="B7" s="150">
-        <x:v>26.8</x:v>
+        <x:v>25.6</x:v>
       </x:c>
       <x:c r="C7" s="150">
-        <x:v>27.9</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="D7" s="150">
-        <x:v>25.5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="151">
-        <x:v>26.8</x:v>
+        <x:v>26.3</x:v>
       </x:c>
       <x:c r="F7" s="152">
-        <x:v>27306</x:v>
+        <x:v>18965</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -8559,19 +8565,19 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B8" s="150">
-        <x:v>26.5</x:v>
+        <x:v>25.7</x:v>
       </x:c>
       <x:c r="C8" s="150">
-        <x:v>30</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="D8" s="150">
-        <x:v>26.1</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="E8" s="151">
-        <x:v>26.6</x:v>
+        <x:v>25.6</x:v>
       </x:c>
       <x:c r="F8" s="152">
-        <x:v>18389</x:v>
+        <x:v>17332</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -8579,19 +8585,19 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B9" s="150">
-        <x:v>27.5</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="C9" s="150">
-        <x:v>27.5</x:v>
+        <x:v>27.9</x:v>
       </x:c>
       <x:c r="D9" s="150">
-        <x:v>24.1</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="E9" s="151">
-        <x:v>25.1</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="F9" s="152">
-        <x:v>14878</x:v>
+        <x:v>27306</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -8599,19 +8605,19 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B10" s="150">
-        <x:v>22.2</x:v>
+        <x:v>26.5</x:v>
       </x:c>
       <x:c r="C10" s="150">
-        <x:v>24.9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="150">
-        <x:v>22.2</x:v>
+        <x:v>26.1</x:v>
       </x:c>
       <x:c r="E10" s="151">
-        <x:v>24.1</x:v>
+        <x:v>26.6</x:v>
       </x:c>
       <x:c r="F10" s="152">
-        <x:v>21752</x:v>
+        <x:v>18389</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -8619,19 +8625,19 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B11" s="150">
-        <x:v>26.4</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="C11" s="150">
-        <x:v>26.7</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="D11" s="150">
-        <x:v>22.2</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="E11" s="151">
-        <x:v>23</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="F11" s="152">
-        <x:v>71199</x:v>
+        <x:v>14878</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -8639,19 +8645,19 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B12" s="150">
-        <x:v>25.8</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="C12" s="150">
-        <x:v>28</x:v>
+        <x:v>24.9</x:v>
       </x:c>
       <x:c r="D12" s="150">
-        <x:v>25.7</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="E12" s="151">
-        <x:v>26</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="F12" s="152">
-        <x:v>30101</x:v>
+        <x:v>21752</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -8659,19 +8665,19 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B13" s="150">
-        <x:v>28</x:v>
+        <x:v>26.4</x:v>
       </x:c>
       <x:c r="C13" s="150">
-        <x:v>28.9</x:v>
+        <x:v>26.7</x:v>
       </x:c>
       <x:c r="D13" s="150">
-        <x:v>25</x:v>
+        <x:v>22.2</x:v>
       </x:c>
       <x:c r="E13" s="151">
-        <x:v>25.7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F13" s="152">
-        <x:v>28960</x:v>
+        <x:v>71199</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -8679,19 +8685,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B14" s="150">
-        <x:v>29.5</x:v>
+        <x:v>25.8</x:v>
       </x:c>
       <x:c r="C14" s="150">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D14" s="150">
-        <x:v>27.8</x:v>
+        <x:v>25.7</x:v>
       </x:c>
       <x:c r="E14" s="151">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F14" s="152">
-        <x:v>24005</x:v>
+        <x:v>30101</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -8699,19 +8705,19 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="B15" s="150">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C15" s="150">
-        <x:v>30</x:v>
+        <x:v>28.9</x:v>
       </x:c>
       <x:c r="D15" s="150">
-        <x:v>28.5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E15" s="151">
-        <x:v>29.5</x:v>
+        <x:v>25.7</x:v>
       </x:c>
       <x:c r="F15" s="152">
-        <x:v>36580</x:v>
+        <x:v>28960</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -8719,19 +8725,19 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="B16" s="150">
-        <x:v>28</x:v>
+        <x:v>29.5</x:v>
       </x:c>
       <x:c r="C16" s="150">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D16" s="150">
+        <x:v>27.8</x:v>
+      </x:c>
+      <x:c r="E16" s="151">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E16" s="151">
-        <x:v>28.7</x:v>
-      </x:c>
       <x:c r="F16" s="152">
-        <x:v>13702</x:v>
+        <x:v>24005</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -8739,19 +8745,19 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B17" s="150">
-        <x:v>28.8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="150">
-        <x:v>30.8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="150">
-        <x:v>27.5</x:v>
+        <x:v>28.5</x:v>
       </x:c>
       <x:c r="E17" s="151">
-        <x:v>28.1</x:v>
+        <x:v>29.5</x:v>
       </x:c>
       <x:c r="F17" s="152">
-        <x:v>18388</x:v>
+        <x:v>36580</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -8759,19 +8765,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B18" s="150">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="150">
-        <x:v>31.3</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D18" s="150">
-        <x:v>27.1</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="151">
-        <x:v>28</x:v>
+        <x:v>28.7</x:v>
       </x:c>
       <x:c r="F18" s="152">
-        <x:v>17902</x:v>
+        <x:v>13702</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -8779,19 +8785,19 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="B19" s="150">
-        <x:v>30.3</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="C19" s="150">
-        <x:v>31.5</x:v>
+        <x:v>30.8</x:v>
       </x:c>
       <x:c r="D19" s="150">
-        <x:v>30.3</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="E19" s="151">
-        <x:v>31</x:v>
+        <x:v>28.1</x:v>
       </x:c>
       <x:c r="F19" s="152">
-        <x:v>15134</x:v>
+        <x:v>18388</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
@@ -8799,19 +8805,19 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B20" s="150">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="150">
-        <x:v>32</x:v>
+        <x:v>31.3</x:v>
       </x:c>
       <x:c r="D20" s="150">
-        <x:v>29</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="E20" s="151">
-        <x:v>29.5</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F20" s="152">
-        <x:v>36162</x:v>
+        <x:v>17902</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -8819,19 +8825,19 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B21" s="150">
-        <x:v>27</x:v>
+        <x:v>30.3</x:v>
       </x:c>
       <x:c r="C21" s="150">
-        <x:v>29.6</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="D21" s="150">
-        <x:v>26</x:v>
+        <x:v>30.3</x:v>
       </x:c>
       <x:c r="E21" s="151">
-        <x:v>28.1</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F21" s="152">
-        <x:v>15336</x:v>
+        <x:v>15134</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -8839,19 +8845,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B22" s="150">
-        <x:v>31.3</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="150">
-        <x:v>32.8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D22" s="150">
-        <x:v>25.5</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E22" s="151">
-        <x:v>26</x:v>
+        <x:v>29.5</x:v>
       </x:c>
       <x:c r="F22" s="152">
-        <x:v>73212</x:v>
+        <x:v>36162</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -8859,19 +8865,19 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B23" s="150">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="150">
-        <x:v>35.6</x:v>
+        <x:v>29.6</x:v>
       </x:c>
       <x:c r="D23" s="150">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="151">
-        <x:v>31.4</x:v>
+        <x:v>28.1</x:v>
       </x:c>
       <x:c r="F23" s="152">
-        <x:v>73636</x:v>
+        <x:v>15336</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -8879,19 +8885,19 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B24" s="150">
-        <x:v>28.8</x:v>
+        <x:v>31.3</x:v>
       </x:c>
       <x:c r="C24" s="150">
-        <x:v>30.7</x:v>
+        <x:v>32.8</x:v>
       </x:c>
       <x:c r="D24" s="150">
-        <x:v>27</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="E24" s="151">
-        <x:v>30.5</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F24" s="152">
-        <x:v>74798</x:v>
+        <x:v>73212</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -8899,19 +8905,19 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B25" s="150">
-        <x:v>33.5</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C25" s="150">
-        <x:v>34</x:v>
+        <x:v>35.6</x:v>
       </x:c>
       <x:c r="D25" s="150">
-        <x:v>28.4</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E25" s="151">
-        <x:v>31.5</x:v>
+        <x:v>31.4</x:v>
       </x:c>
       <x:c r="F25" s="152">
-        <x:v>71037</x:v>
+        <x:v>73636</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -8919,19 +8925,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B26" s="150">
-        <x:v>38</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="C26" s="150">
-        <x:v>40.5</x:v>
+        <x:v>30.7</x:v>
       </x:c>
       <x:c r="D26" s="150">
         <x:v>27</x:v>
       </x:c>
       <x:c r="E26" s="151">
-        <x:v>34</x:v>
+        <x:v>30.5</x:v>
       </x:c>
       <x:c r="F26" s="152">
-        <x:v>235859</x:v>
+        <x:v>74798</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
@@ -8939,19 +8945,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B27" s="150">
-        <x:v>42.3</x:v>
+        <x:v>33.5</x:v>
       </x:c>
       <x:c r="C27" s="150">
-        <x:v>44.4</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D27" s="150">
-        <x:v>34.1</x:v>
+        <x:v>28.4</x:v>
       </x:c>
       <x:c r="E27" s="151">
-        <x:v>38</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="F27" s="152">
-        <x:v>194563</x:v>
+        <x:v>71037</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
@@ -8962,16 +8968,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C28" s="150">
-        <x:v>42.5</x:v>
+        <x:v>40.5</x:v>
       </x:c>
       <x:c r="D28" s="150">
-        <x:v>37.6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E28" s="151">
-        <x:v>41.1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F28" s="152">
-        <x:v>86803</x:v>
+        <x:v>235859</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -8979,19 +8985,19 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B29" s="150">
-        <x:v>36.5</x:v>
+        <x:v>42.3</x:v>
       </x:c>
       <x:c r="C29" s="150">
-        <x:v>39.8</x:v>
+        <x:v>44.4</x:v>
       </x:c>
       <x:c r="D29" s="150">
-        <x:v>36.5</x:v>
+        <x:v>34.1</x:v>
       </x:c>
       <x:c r="E29" s="151">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F29" s="152">
-        <x:v>96298</x:v>
+        <x:v>194563</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -8999,19 +9005,19 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B30" s="150">
-        <x:v>31.5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="150">
-        <x:v>35.4</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="D30" s="150">
-        <x:v>31.5</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="E30" s="151">
-        <x:v>35</x:v>
+        <x:v>41.1</x:v>
       </x:c>
       <x:c r="F30" s="152">
-        <x:v>132134</x:v>
+        <x:v>86803</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -9019,19 +9025,19 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B31" s="150">
-        <x:v>30.2</x:v>
+        <x:v>36.5</x:v>
       </x:c>
       <x:c r="C31" s="150">
-        <x:v>32</x:v>
+        <x:v>39.8</x:v>
       </x:c>
       <x:c r="D31" s="150">
-        <x:v>26.8</x:v>
+        <x:v>36.5</x:v>
       </x:c>
       <x:c r="E31" s="151">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="152">
-        <x:v>85369</x:v>
+        <x:v>96298</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -9039,19 +9045,19 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B32" s="150">
-        <x:v>27.1</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="C32" s="150">
-        <x:v>33.6</x:v>
+        <x:v>35.4</x:v>
       </x:c>
       <x:c r="D32" s="150">
-        <x:v>27.1</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="E32" s="151">
-        <x:v>30.1</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F32" s="152">
-        <x:v>299500</x:v>
+        <x:v>132134</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -9059,19 +9065,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B33" s="150">
-        <x:v>22</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C33" s="150">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D33" s="150">
-        <x:v>21</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="E33" s="151">
-        <x:v>26.7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F33" s="152">
-        <x:v>197592</x:v>
+        <x:v>85369</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
@@ -9079,19 +9085,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B34" s="150">
-        <x:v>21.9</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C34" s="150">
-        <x:v>21.9</x:v>
+        <x:v>33.6</x:v>
       </x:c>
       <x:c r="D34" s="150">
-        <x:v>19.05</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="E34" s="151">
-        <x:v>21</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="F34" s="152">
-        <x:v>91002</x:v>
+        <x:v>299500</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
@@ -9099,19 +9105,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B35" s="150">
-        <x:v>21.7</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C35" s="150">
-        <x:v>21.9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D35" s="150">
-        <x:v>21.1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E35" s="151">
-        <x:v>21.2</x:v>
+        <x:v>26.7</x:v>
       </x:c>
       <x:c r="F35" s="152">
-        <x:v>24885</x:v>
+        <x:v>197592</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -9119,19 +9125,19 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B36" s="150">
-        <x:v>20.8</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="C36" s="150">
-        <x:v>22</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="D36" s="150">
-        <x:v>20.8</x:v>
+        <x:v>19.05</x:v>
       </x:c>
       <x:c r="E36" s="151">
-        <x:v>21.7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F36" s="152">
-        <x:v>34946</x:v>
+        <x:v>91002</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -9139,19 +9145,19 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B37" s="150">
-        <x:v>19.3</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="C37" s="150">
-        <x:v>21.8</x:v>
+        <x:v>21.9</x:v>
       </x:c>
       <x:c r="D37" s="150">
-        <x:v>19.3</x:v>
+        <x:v>21.1</x:v>
       </x:c>
       <x:c r="E37" s="151">
-        <x:v>20.8</x:v>
+        <x:v>21.2</x:v>
       </x:c>
       <x:c r="F37" s="152">
-        <x:v>43227</x:v>
+        <x:v>24885</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -9159,19 +9165,19 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B38" s="150">
-        <x:v>19.3</x:v>
+        <x:v>20.8</x:v>
       </x:c>
       <x:c r="C38" s="150">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D38" s="150">
-        <x:v>18.8</x:v>
+        <x:v>20.8</x:v>
       </x:c>
       <x:c r="E38" s="151">
-        <x:v>19</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="F38" s="152">
-        <x:v>41077</x:v>
+        <x:v>34946</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -9179,19 +9185,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B39" s="150">
-        <x:v>20.9</x:v>
+        <x:v>19.3</x:v>
       </x:c>
       <x:c r="C39" s="150">
-        <x:v>22.6</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="D39" s="150">
-        <x:v>20</x:v>
+        <x:v>19.3</x:v>
       </x:c>
       <x:c r="E39" s="151">
         <x:v>20.8</x:v>
       </x:c>
       <x:c r="F39" s="152">
-        <x:v>27977</x:v>
+        <x:v>43227</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
@@ -9199,19 +9205,19 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B40" s="150">
+        <x:v>19.3</x:v>
+      </x:c>
+      <x:c r="C40" s="150">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C40" s="150">
-        <x:v>23.6</x:v>
-      </x:c>
       <x:c r="D40" s="150">
-        <x:v>20.1</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="E40" s="151">
-        <x:v>20.9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F40" s="152">
-        <x:v>26938</x:v>
+        <x:v>41077</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
@@ -9219,19 +9225,19 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B41" s="150">
-        <x:v>21.1</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C41" s="150">
-        <x:v>21.7</x:v>
+        <x:v>22.6</x:v>
       </x:c>
       <x:c r="D41" s="150">
-        <x:v>18.3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E41" s="151">
-        <x:v>20.6</x:v>
+        <x:v>20.8</x:v>
       </x:c>
       <x:c r="F41" s="152">
-        <x:v>20660</x:v>
+        <x:v>27977</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -9239,19 +9245,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B42" s="150">
-        <x:v>23.5</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C42" s="150">
-        <x:v>23.7</x:v>
+        <x:v>23.6</x:v>
       </x:c>
       <x:c r="D42" s="150">
-        <x:v>18.8</x:v>
+        <x:v>20.1</x:v>
       </x:c>
       <x:c r="E42" s="151">
-        <x:v>20.5</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="F42" s="152">
-        <x:v>78650</x:v>
+        <x:v>26938</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
@@ -9259,19 +9265,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="B43" s="150">
-        <x:v>20.2</x:v>
+        <x:v>21.1</x:v>
       </x:c>
       <x:c r="C43" s="150">
-        <x:v>25.5</x:v>
+        <x:v>21.7</x:v>
       </x:c>
       <x:c r="D43" s="150">
-        <x:v>20.2</x:v>
+        <x:v>18.3</x:v>
       </x:c>
       <x:c r="E43" s="151">
-        <x:v>23</x:v>
+        <x:v>20.6</x:v>
       </x:c>
       <x:c r="F43" s="152">
-        <x:v>208252</x:v>
+        <x:v>20660</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6">
@@ -9279,19 +9285,19 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B44" s="150">
-        <x:v>18</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="C44" s="150">
-        <x:v>20.7</x:v>
+        <x:v>23.7</x:v>
       </x:c>
       <x:c r="D44" s="150">
-        <x:v>17.2</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="E44" s="151">
-        <x:v>20.2</x:v>
+        <x:v>20.5</x:v>
       </x:c>
       <x:c r="F44" s="152">
-        <x:v>36367</x:v>
+        <x:v>78650</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -9299,19 +9305,19 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="B45" s="150">
-        <x:v>19.2</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="C45" s="150">
-        <x:v>19.2</x:v>
+        <x:v>25.5</x:v>
       </x:c>
       <x:c r="D45" s="150">
-        <x:v>16.7</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="E45" s="151">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F45" s="152">
-        <x:v>16671</x:v>
+        <x:v>208252</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -9322,16 +9328,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C46" s="150">
-        <x:v>19.5</x:v>
+        <x:v>20.7</x:v>
       </x:c>
       <x:c r="D46" s="150">
-        <x:v>18</x:v>
+        <x:v>17.2</x:v>
       </x:c>
       <x:c r="E46" s="151">
-        <x:v>19.2</x:v>
+        <x:v>20.2</x:v>
       </x:c>
       <x:c r="F46" s="152">
-        <x:v>27319</x:v>
+        <x:v>36367</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:6">
@@ -9339,19 +9345,19 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B47" s="150">
-        <x:v>19</x:v>
+        <x:v>19.2</x:v>
       </x:c>
       <x:c r="C47" s="150">
-        <x:v>19.6</x:v>
+        <x:v>19.2</x:v>
       </x:c>
       <x:c r="D47" s="150">
-        <x:v>17.55</x:v>
+        <x:v>16.7</x:v>
       </x:c>
       <x:c r="E47" s="151">
-        <x:v>17.7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F47" s="152">
-        <x:v>17355</x:v>
+        <x:v>16671</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
@@ -9359,19 +9365,19 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B48" s="150">
-        <x:v>16.95</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C48" s="150">
-        <x:v>18.7</x:v>
+        <x:v>19.5</x:v>
       </x:c>
       <x:c r="D48" s="150">
-        <x:v>16.5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E48" s="151">
-        <x:v>17.6</x:v>
+        <x:v>19.2</x:v>
       </x:c>
       <x:c r="F48" s="152">
-        <x:v>43493</x:v>
+        <x:v>27319</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -9379,19 +9385,19 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="B49" s="150">
-        <x:v>16.95</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C49" s="150">
-        <x:v>16.95</x:v>
+        <x:v>19.6</x:v>
       </x:c>
       <x:c r="D49" s="150">
-        <x:v>16.9</x:v>
+        <x:v>17.55</x:v>
       </x:c>
       <x:c r="E49" s="151">
-        <x:v>16.9</x:v>
+        <x:v>17.7</x:v>
       </x:c>
       <x:c r="F49" s="152">
-        <x:v>700</x:v>
+        <x:v>17355</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -9402,16 +9408,16 @@
         <x:v>16.95</x:v>
       </x:c>
       <x:c r="C50" s="150">
-        <x:v>16.95</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="D50" s="150">
-        <x:v>14.65</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E50" s="151">
-        <x:v>16.7</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="F50" s="152">
-        <x:v>13129</x:v>
+        <x:v>43493</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
@@ -9419,19 +9425,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="B51" s="150">
-        <x:v>17.3</x:v>
+        <x:v>16.95</x:v>
       </x:c>
       <x:c r="C51" s="150">
-        <x:v>17.3</x:v>
+        <x:v>16.95</x:v>
       </x:c>
       <x:c r="D51" s="150">
-        <x:v>16.5</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="E51" s="151">
-        <x:v>17</x:v>
+        <x:v>16.9</x:v>
       </x:c>
       <x:c r="F51" s="152">
-        <x:v>1561</x:v>
+        <x:v>700</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -9439,19 +9445,19 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="B52" s="150">
-        <x:v>17.35</x:v>
+        <x:v>16.95</x:v>
       </x:c>
       <x:c r="C52" s="150">
-        <x:v>17.35</x:v>
+        <x:v>16.95</x:v>
       </x:c>
       <x:c r="D52" s="150">
-        <x:v>16.5</x:v>
+        <x:v>14.65</x:v>
       </x:c>
       <x:c r="E52" s="151">
-        <x:v>17.3</x:v>
+        <x:v>16.7</x:v>
       </x:c>
       <x:c r="F52" s="152">
-        <x:v>7288</x:v>
+        <x:v>13129</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -9459,19 +9465,19 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B53" s="150">
-        <x:v>17.8</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="C53" s="150">
-        <x:v>17.8</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="D53" s="150">
-        <x:v>16.1</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E53" s="151">
-        <x:v>17.3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F53" s="152">
-        <x:v>22419</x:v>
+        <x:v>1561</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -9479,19 +9485,19 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B54" s="150">
-        <x:v>16.45</x:v>
+        <x:v>17.35</x:v>
       </x:c>
       <x:c r="C54" s="150">
-        <x:v>18.7</x:v>
+        <x:v>17.35</x:v>
       </x:c>
       <x:c r="D54" s="150">
-        <x:v>15.5</x:v>
+        <x:v>16.5</x:v>
       </x:c>
       <x:c r="E54" s="151">
-        <x:v>17.25</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="F54" s="152">
-        <x:v>41648</x:v>
+        <x:v>7288</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -9499,19 +9505,19 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B55" s="150">
-        <x:v>14.25</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="C55" s="150">
-        <x:v>16.7</x:v>
+        <x:v>17.8</x:v>
       </x:c>
       <x:c r="D55" s="150">
-        <x:v>14.25</x:v>
+        <x:v>16.1</x:v>
       </x:c>
       <x:c r="E55" s="151">
-        <x:v>16.45</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="F55" s="152">
-        <x:v>29730</x:v>
+        <x:v>22419</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -9519,19 +9525,19 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B56" s="150">
-        <x:v>14</x:v>
+        <x:v>16.45</x:v>
       </x:c>
       <x:c r="C56" s="150">
-        <x:v>14.25</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="D56" s="150">
-        <x:v>12.8</x:v>
+        <x:v>15.5</x:v>
       </x:c>
       <x:c r="E56" s="151">
-        <x:v>13.5</x:v>
+        <x:v>17.25</x:v>
       </x:c>
       <x:c r="F56" s="152">
-        <x:v>11962</x:v>
+        <x:v>41648</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
@@ -9539,19 +9545,19 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="B57" s="150">
-        <x:v>14.9</x:v>
+        <x:v>14.25</x:v>
       </x:c>
       <x:c r="C57" s="150">
-        <x:v>14.9</x:v>
+        <x:v>16.7</x:v>
       </x:c>
       <x:c r="D57" s="150">
-        <x:v>13.5</x:v>
+        <x:v>14.25</x:v>
       </x:c>
       <x:c r="E57" s="151">
-        <x:v>14</x:v>
+        <x:v>16.45</x:v>
       </x:c>
       <x:c r="F57" s="152">
-        <x:v>14757</x:v>
+        <x:v>29730</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
@@ -9559,19 +9565,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B58" s="150">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="150">
-        <x:v>14.7</x:v>
+        <x:v>14.25</x:v>
       </x:c>
       <x:c r="D58" s="150">
-        <x:v>12</x:v>
+        <x:v>12.8</x:v>
       </x:c>
       <x:c r="E58" s="151">
         <x:v>13.5</x:v>
       </x:c>
       <x:c r="F58" s="152">
-        <x:v>50104</x:v>
+        <x:v>11962</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -9579,19 +9585,19 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B59" s="150">
-        <x:v>11.5</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="C59" s="150">
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="D59" s="150">
         <x:v>13.5</x:v>
       </x:c>
-      <x:c r="D59" s="150">
-        <x:v>11.5</x:v>
-      </x:c>
       <x:c r="E59" s="151">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F59" s="152">
-        <x:v>20551</x:v>
+        <x:v>14757</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -9599,19 +9605,19 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="B60" s="150">
-        <x:v>11.4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C60" s="150">
+        <x:v>14.7</x:v>
+      </x:c>
+      <x:c r="D60" s="150">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D60" s="150">
-        <x:v>10.35</x:v>
-      </x:c>
       <x:c r="E60" s="151">
-        <x:v>11.7</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="F60" s="152">
-        <x:v>56452</x:v>
+        <x:v>50104</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -9619,19 +9625,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B61" s="150">
-        <x:v>12.4</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="C61" s="150">
-        <x:v>12.4</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="D61" s="150">
-        <x:v>10.3</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="E61" s="151">
-        <x:v>11.45</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F61" s="152">
-        <x:v>43305</x:v>
+        <x:v>20551</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -9639,19 +9645,19 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B62" s="150">
-        <x:v>10.1</x:v>
+        <x:v>11.4</x:v>
       </x:c>
       <x:c r="C62" s="150">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D62" s="150">
-        <x:v>9.38</x:v>
+        <x:v>10.35</x:v>
       </x:c>
       <x:c r="E62" s="151">
-        <x:v>11</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="F62" s="152">
-        <x:v>36817</x:v>
+        <x:v>56452</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -9659,19 +9665,19 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B63" s="150">
-        <x:v>10</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="C63" s="150">
-        <x:v>10.1</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D63" s="150">
-        <x:v>9.3</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="E63" s="151">
-        <x:v>9.8</x:v>
+        <x:v>11.45</x:v>
       </x:c>
       <x:c r="F63" s="152">
-        <x:v>37629</x:v>
+        <x:v>43305</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -9679,19 +9685,19 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B64" s="150">
-        <x:v>10.15</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="C64" s="150">
-        <x:v>10.15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D64" s="150">
-        <x:v>9.5</x:v>
+        <x:v>9.38</x:v>
       </x:c>
       <x:c r="E64" s="151">
-        <x:v>9.98</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="152">
-        <x:v>17838</x:v>
+        <x:v>36817</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
@@ -9699,19 +9705,19 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B65" s="150">
-        <x:v>10.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C65" s="150">
-        <x:v>10.7</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="D65" s="150">
-        <x:v>9.36</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E65" s="151">
-        <x:v>10.1</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="F65" s="152">
-        <x:v>15500</x:v>
+        <x:v>37629</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -9719,19 +9725,19 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B66" s="150">
-        <x:v>10.45</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="C66" s="150">
-        <x:v>10.7</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="D66" s="150">
-        <x:v>9.76</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="E66" s="151">
-        <x:v>10</x:v>
+        <x:v>9.98</x:v>
       </x:c>
       <x:c r="F66" s="152">
-        <x:v>18724</x:v>
+        <x:v>17838</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -9739,19 +9745,19 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B67" s="150">
-        <x:v>10.5</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="C67" s="150">
-        <x:v>10.6</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="D67" s="150">
-        <x:v>9.6</x:v>
+        <x:v>9.36</x:v>
       </x:c>
       <x:c r="E67" s="151">
-        <x:v>10.5</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="F67" s="152">
-        <x:v>6631</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -9759,19 +9765,19 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B68" s="150">
+        <x:v>10.45</x:v>
+      </x:c>
+      <x:c r="C68" s="150">
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="D68" s="150">
+        <x:v>9.76</x:v>
+      </x:c>
+      <x:c r="E68" s="151">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C68" s="150">
-        <x:v>11.35</x:v>
-      </x:c>
-      <x:c r="D68" s="150">
-        <x:v>9.92</x:v>
-      </x:c>
-      <x:c r="E68" s="151">
-        <x:v>10.65</x:v>
-      </x:c>
       <x:c r="F68" s="152">
-        <x:v>6125</x:v>
+        <x:v>18724</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -9779,19 +9785,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B69" s="150">
-        <x:v>10.35</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="C69" s="150">
-        <x:v>10.35</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="D69" s="150">
-        <x:v>9.5</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="E69" s="151">
-        <x:v>9.96</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="F69" s="152">
-        <x:v>21961</x:v>
+        <x:v>6631</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6">
@@ -9799,19 +9805,19 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B70" s="150">
-        <x:v>10.3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C70" s="150">
-        <x:v>10.3</x:v>
+        <x:v>11.35</x:v>
       </x:c>
       <x:c r="D70" s="150">
-        <x:v>9.46</x:v>
+        <x:v>9.92</x:v>
       </x:c>
       <x:c r="E70" s="151">
-        <x:v>10.2</x:v>
+        <x:v>10.65</x:v>
       </x:c>
       <x:c r="F70" s="152">
-        <x:v>7207</x:v>
+        <x:v>6125</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
@@ -9819,19 +9825,19 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B71" s="150">
-        <x:v>10.95</x:v>
+        <x:v>10.35</x:v>
       </x:c>
       <x:c r="C71" s="150">
-        <x:v>10.95</x:v>
+        <x:v>10.35</x:v>
       </x:c>
       <x:c r="D71" s="150">
-        <x:v>9.84</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="E71" s="151">
-        <x:v>10.3</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="F71" s="152">
-        <x:v>14433</x:v>
+        <x:v>21961</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -9839,19 +9845,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B72" s="150">
-        <x:v>10.15</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="C72" s="150">
-        <x:v>10.85</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="D72" s="150">
-        <x:v>9.7</x:v>
+        <x:v>9.46</x:v>
       </x:c>
       <x:c r="E72" s="151">
-        <x:v>10.8</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="F72" s="152">
-        <x:v>45330</x:v>
+        <x:v>7207</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
@@ -9859,19 +9865,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B73" s="150">
-        <x:v>10</x:v>
+        <x:v>10.95</x:v>
       </x:c>
       <x:c r="C73" s="150">
-        <x:v>10.85</x:v>
+        <x:v>10.95</x:v>
       </x:c>
       <x:c r="D73" s="150">
         <x:v>9.84</x:v>
       </x:c>
       <x:c r="E73" s="151">
-        <x:v>10.15</x:v>
+        <x:v>10.3</x:v>
       </x:c>
       <x:c r="F73" s="152">
-        <x:v>5492</x:v>
+        <x:v>14433</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
@@ -9879,19 +9885,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B74" s="150">
-        <x:v>10.1</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="C74" s="150">
-        <x:v>11.3</x:v>
+        <x:v>10.85</x:v>
       </x:c>
       <x:c r="D74" s="150">
         <x:v>9.7</x:v>
       </x:c>
       <x:c r="E74" s="151">
-        <x:v>10.05</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="F74" s="152">
-        <x:v>17894</x:v>
+        <x:v>45330</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -9899,19 +9905,19 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="B75" s="150">
-        <x:v>10.1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C75" s="150">
-        <x:v>11.35</x:v>
+        <x:v>10.85</x:v>
       </x:c>
       <x:c r="D75" s="150">
-        <x:v>9.6</x:v>
+        <x:v>9.84</x:v>
       </x:c>
       <x:c r="E75" s="151">
-        <x:v>10.2</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="F75" s="152">
-        <x:v>20453</x:v>
+        <x:v>5492</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -9919,19 +9925,19 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B76" s="150">
-        <x:v>9.8</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="C76" s="150">
-        <x:v>10.15</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="D76" s="150">
-        <x:v>9.8</x:v>
+        <x:v>9.7</x:v>
       </x:c>
       <x:c r="E76" s="151">
-        <x:v>10.1</x:v>
+        <x:v>10.05</x:v>
       </x:c>
       <x:c r="F76" s="152">
-        <x:v>12400</x:v>
+        <x:v>17894</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:6">
@@ -9939,19 +9945,19 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B77" s="150">
-        <x:v>10.5</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="C77" s="150">
-        <x:v>10.5</x:v>
+        <x:v>11.35</x:v>
       </x:c>
       <x:c r="D77" s="150">
-        <x:v>9.8</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="E77" s="151">
-        <x:v>9.82</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="F77" s="152">
-        <x:v>13016</x:v>
+        <x:v>20453</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6">
@@ -9959,19 +9965,19 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B78" s="150">
-        <x:v>10.6</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="C78" s="150">
-        <x:v>10.6</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="D78" s="150">
-        <x:v>9.54</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="E78" s="151">
         <x:v>10.1</x:v>
       </x:c>
       <x:c r="F78" s="152">
-        <x:v>11981</x:v>
+        <x:v>12400</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
@@ -9979,19 +9985,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B79" s="150">
-        <x:v>11.1</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="C79" s="150">
-        <x:v>11.1</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="D79" s="150">
-        <x:v>9.52</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="E79" s="151">
-        <x:v>9.88</x:v>
+        <x:v>9.82</x:v>
       </x:c>
       <x:c r="F79" s="152">
-        <x:v>27650</x:v>
+        <x:v>13016</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6">
@@ -9999,19 +10005,19 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B80" s="150">
-        <x:v>9.8</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="C80" s="150">
-        <x:v>10.75</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="D80" s="150">
-        <x:v>9.3</x:v>
+        <x:v>9.54</x:v>
       </x:c>
       <x:c r="E80" s="151">
-        <x:v>9.68</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="F80" s="152">
-        <x:v>24379</x:v>
+        <x:v>11981</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:6">
@@ -10019,19 +10025,19 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B81" s="150">
-        <x:v>11.35</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="C81" s="150">
-        <x:v>11.35</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="D81" s="150">
-        <x:v>9.5</x:v>
+        <x:v>9.52</x:v>
       </x:c>
       <x:c r="E81" s="151">
-        <x:v>9.6</x:v>
+        <x:v>9.88</x:v>
       </x:c>
       <x:c r="F81" s="152">
-        <x:v>51722</x:v>
+        <x:v>27650</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:6">
@@ -10039,19 +10045,19 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="B82" s="150">
-        <x:v>9.94</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="C82" s="150">
-        <x:v>10.95</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="D82" s="150">
-        <x:v>9.8</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E82" s="151">
-        <x:v>10.35</x:v>
+        <x:v>9.68</x:v>
       </x:c>
       <x:c r="F82" s="152">
-        <x:v>38884</x:v>
+        <x:v>24379</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:6">
@@ -10059,19 +10065,19 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B83" s="150">
-        <x:v>11.6</x:v>
+        <x:v>11.35</x:v>
       </x:c>
       <x:c r="C83" s="150">
-        <x:v>11.6</x:v>
+        <x:v>11.35</x:v>
       </x:c>
       <x:c r="D83" s="150">
-        <x:v>9.36</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="E83" s="151">
-        <x:v>9.94</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="F83" s="152">
-        <x:v>23468</x:v>
+        <x:v>51722</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:6">
@@ -10079,19 +10085,19 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="B84" s="150">
-        <x:v>9.9</x:v>
+        <x:v>9.94</x:v>
       </x:c>
       <x:c r="C84" s="150">
-        <x:v>11.5</x:v>
+        <x:v>10.95</x:v>
       </x:c>
       <x:c r="D84" s="150">
-        <x:v>9.32</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="E84" s="151">
-        <x:v>11.5</x:v>
+        <x:v>10.35</x:v>
       </x:c>
       <x:c r="F84" s="152">
-        <x:v>40376</x:v>
+        <x:v>38884</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:6">
@@ -10099,19 +10105,19 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="B85" s="150">
-        <x:v>9.38</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="C85" s="150">
-        <x:v>9.96</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="D85" s="150">
-        <x:v>9.38</x:v>
+        <x:v>9.36</x:v>
       </x:c>
       <x:c r="E85" s="151">
-        <x:v>9.96</x:v>
+        <x:v>9.94</x:v>
       </x:c>
       <x:c r="F85" s="152">
-        <x:v>17237</x:v>
+        <x:v>23468</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:6">
@@ -10119,19 +10125,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B86" s="150">
-        <x:v>10.1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="C86" s="150">
-        <x:v>10.25</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="D86" s="150">
-        <x:v>9.3</x:v>
+        <x:v>9.32</x:v>
       </x:c>
       <x:c r="E86" s="151">
-        <x:v>9.38</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="F86" s="152">
-        <x:v>36075</x:v>
+        <x:v>40376</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6">
@@ -10139,19 +10145,19 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B87" s="150">
-        <x:v>10.6</x:v>
+        <x:v>9.38</x:v>
       </x:c>
       <x:c r="C87" s="150">
-        <x:v>11.15</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="D87" s="150">
-        <x:v>9.46</x:v>
+        <x:v>9.38</x:v>
       </x:c>
       <x:c r="E87" s="151">
-        <x:v>10.75</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="F87" s="152">
-        <x:v>13857</x:v>
+        <x:v>17237</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:6">
@@ -10159,19 +10165,19 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="B88" s="150">
-        <x:v>9.5</x:v>
+        <x:v>10.1</x:v>
       </x:c>
       <x:c r="C88" s="150">
-        <x:v>10.65</x:v>
+        <x:v>10.25</x:v>
       </x:c>
       <x:c r="D88" s="150">
         <x:v>9.3</x:v>
       </x:c>
       <x:c r="E88" s="151">
-        <x:v>10.65</x:v>
+        <x:v>9.38</x:v>
       </x:c>
       <x:c r="F88" s="152">
-        <x:v>14041</x:v>
+        <x:v>36075</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:6">
@@ -10179,19 +10185,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="B89" s="150">
-        <x:v>10</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="C89" s="150">
-        <x:v>10</x:v>
+        <x:v>11.15</x:v>
       </x:c>
       <x:c r="D89" s="150">
-        <x:v>9.26</x:v>
+        <x:v>9.46</x:v>
       </x:c>
       <x:c r="E89" s="151">
-        <x:v>9.5</x:v>
+        <x:v>10.75</x:v>
       </x:c>
       <x:c r="F89" s="152">
-        <x:v>22699</x:v>
+        <x:v>13857</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:6">
@@ -10202,16 +10208,16 @@
         <x:v>9.5</x:v>
       </x:c>
       <x:c r="C90" s="150">
-        <x:v>10.45</x:v>
+        <x:v>10.65</x:v>
       </x:c>
       <x:c r="D90" s="150">
-        <x:v>9.5</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="E90" s="151">
-        <x:v>10.2</x:v>
+        <x:v>10.65</x:v>
       </x:c>
       <x:c r="F90" s="152">
-        <x:v>2686</x:v>
+        <x:v>14041</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:6">
@@ -10219,19 +10225,19 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B91" s="150">
-        <x:v>9.74</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C91" s="150">
-        <x:v>12.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D91" s="150">
-        <x:v>9.42</x:v>
+        <x:v>9.26</x:v>
       </x:c>
       <x:c r="E91" s="151">
-        <x:v>9.6</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="F91" s="152">
-        <x:v>20003</x:v>
+        <x:v>22699</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:6">
@@ -10239,19 +10245,19 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B92" s="150">
-        <x:v>9.74</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="C92" s="150">
-        <x:v>10.4</x:v>
+        <x:v>10.45</x:v>
       </x:c>
       <x:c r="D92" s="150">
-        <x:v>9.22</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="E92" s="151">
-        <x:v>9.34</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="F92" s="152">
-        <x:v>22057</x:v>
+        <x:v>2686</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:6">
@@ -10259,19 +10265,19 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B93" s="150">
-        <x:v>10.4</x:v>
+        <x:v>9.74</x:v>
       </x:c>
       <x:c r="C93" s="150">
-        <x:v>10.4</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="D93" s="150">
-        <x:v>9.74</x:v>
+        <x:v>9.42</x:v>
       </x:c>
       <x:c r="E93" s="151">
-        <x:v>10.15</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="F93" s="152">
-        <x:v>12312</x:v>
+        <x:v>20003</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:6">
@@ -10279,19 +10285,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B94" s="150">
-        <x:v>10.25</x:v>
+        <x:v>9.74</x:v>
       </x:c>
       <x:c r="C94" s="150">
-        <x:v>10.65</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="D94" s="150">
-        <x:v>10.25</x:v>
+        <x:v>9.22</x:v>
       </x:c>
       <x:c r="E94" s="151">
-        <x:v>10.6</x:v>
+        <x:v>9.34</x:v>
       </x:c>
       <x:c r="F94" s="152">
-        <x:v>9881</x:v>
+        <x:v>22057</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:6">
@@ -10299,19 +10305,19 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B95" s="150">
-        <x:v>11</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="C95" s="150">
-        <x:v>12.5</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="D95" s="150">
-        <x:v>10.6</x:v>
+        <x:v>9.74</x:v>
       </x:c>
       <x:c r="E95" s="151">
-        <x:v>10.65</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="F95" s="152">
-        <x:v>18406</x:v>
+        <x:v>12312</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:6">
@@ -10319,19 +10325,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="B96" s="150">
-        <x:v>11</x:v>
+        <x:v>10.25</x:v>
       </x:c>
       <x:c r="C96" s="150">
-        <x:v>11.45</x:v>
+        <x:v>10.65</x:v>
       </x:c>
       <x:c r="D96" s="150">
-        <x:v>10.45</x:v>
+        <x:v>10.25</x:v>
       </x:c>
       <x:c r="E96" s="151">
-        <x:v>11</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="F96" s="152">
-        <x:v>6988</x:v>
+        <x:v>9881</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:6">
@@ -10339,19 +10345,19 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B97" s="150">
-        <x:v>11.35</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C97" s="150">
-        <x:v>11.4</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="D97" s="150">
-        <x:v>10.45</x:v>
+        <x:v>10.6</x:v>
       </x:c>
       <x:c r="E97" s="151">
-        <x:v>11.3</x:v>
+        <x:v>10.65</x:v>
       </x:c>
       <x:c r="F97" s="152">
-        <x:v>13970</x:v>
+        <x:v>18406</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:6">
@@ -10359,19 +10365,19 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B98" s="150">
-        <x:v>11.9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C98" s="150">
-        <x:v>11.9</x:v>
+        <x:v>11.45</x:v>
       </x:c>
       <x:c r="D98" s="150">
-        <x:v>10.35</x:v>
+        <x:v>10.45</x:v>
       </x:c>
       <x:c r="E98" s="151">
-        <x:v>11.85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F98" s="152">
-        <x:v>11264</x:v>
+        <x:v>6988</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:6">
@@ -10379,19 +10385,19 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B99" s="150">
-        <x:v>10.9</x:v>
+        <x:v>11.35</x:v>
       </x:c>
       <x:c r="C99" s="150">
-        <x:v>12</x:v>
+        <x:v>11.4</x:v>
       </x:c>
       <x:c r="D99" s="150">
-        <x:v>10.15</x:v>
+        <x:v>10.45</x:v>
       </x:c>
       <x:c r="E99" s="151">
-        <x:v>11.9</x:v>
+        <x:v>11.3</x:v>
       </x:c>
       <x:c r="F99" s="152">
-        <x:v>80095</x:v>
+        <x:v>13970</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:6">
@@ -10399,19 +10405,19 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B100" s="150">
-        <x:v>12.6</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="C100" s="150">
-        <x:v>12.6</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="D100" s="150">
-        <x:v>9.8</x:v>
+        <x:v>10.35</x:v>
       </x:c>
       <x:c r="E100" s="151">
-        <x:v>9.86</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="F100" s="152">
-        <x:v>102697</x:v>
+        <x:v>11264</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:6">
@@ -10419,19 +10425,19 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="B101" s="150">
-        <x:v>10.7</x:v>
+        <x:v>10.9</x:v>
       </x:c>
       <x:c r="C101" s="150">
-        <x:v>13.2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D101" s="150">
-        <x:v>10.7</x:v>
+        <x:v>10.15</x:v>
       </x:c>
       <x:c r="E101" s="151">
-        <x:v>12</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="F101" s="152">
-        <x:v>5120</x:v>
+        <x:v>80095</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:6">
@@ -10439,19 +10445,19 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="B102" s="150">
-        <x:v>10.8</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C102" s="150">
-        <x:v>11.7</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="D102" s="150">
-        <x:v>10.8</x:v>
+        <x:v>9.8</x:v>
       </x:c>
       <x:c r="E102" s="151">
-        <x:v>10.8</x:v>
+        <x:v>9.86</x:v>
       </x:c>
       <x:c r="F102" s="152">
-        <x:v>14183</x:v>
+        <x:v>102697</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:6">
@@ -10459,19 +10465,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B103" s="150">
-        <x:v>12.1</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="C103" s="150">
-        <x:v>12.1</x:v>
+        <x:v>13.2</x:v>
       </x:c>
       <x:c r="D103" s="150">
-        <x:v>10.65</x:v>
+        <x:v>10.7</x:v>
       </x:c>
       <x:c r="E103" s="151">
-        <x:v>10.8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F103" s="152">
-        <x:v>28293</x:v>
+        <x:v>5120</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:6">
@@ -10479,19 +10485,19 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="B104" s="150">
-        <x:v>12.5</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="C104" s="150">
-        <x:v>12.5</x:v>
+        <x:v>11.7</x:v>
       </x:c>
       <x:c r="D104" s="150">
-        <x:v>12</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="E104" s="151">
-        <x:v>12.2</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="F104" s="152">
-        <x:v>4715</x:v>
+        <x:v>14183</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:6">
@@ -10499,19 +10505,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="B105" s="150">
-        <x:v>12.75</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C105" s="150">
-        <x:v>12.75</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="D105" s="150">
-        <x:v>12</x:v>
+        <x:v>10.65</x:v>
       </x:c>
       <x:c r="E105" s="151">
-        <x:v>12.5</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="F105" s="152">
-        <x:v>6665</x:v>
+        <x:v>28293</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:6">
@@ -10519,19 +10525,19 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B106" s="150">
-        <x:v>12.9</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="C106" s="150">
-        <x:v>12.9</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="D106" s="150">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E106" s="151">
-        <x:v>12.75</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="F106" s="152">
-        <x:v>12483</x:v>
+        <x:v>4715</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:6">
@@ -10539,19 +10545,19 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B107" s="150">
-        <x:v>13.05</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="C107" s="150">
-        <x:v>13.05</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="D107" s="150">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E107" s="151">
-        <x:v>12.9</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="F107" s="152">
-        <x:v>18841</x:v>
+        <x:v>6665</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:6">
@@ -10559,19 +10565,19 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="B108" s="150">
-        <x:v>13.9</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="C108" s="150">
-        <x:v>13.9</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="D108" s="150">
-        <x:v>12.9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E108" s="151">
-        <x:v>13.05</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="F108" s="152">
-        <x:v>9310</x:v>
+        <x:v>12483</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:6">
@@ -10579,19 +10585,19 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B109" s="150">
-        <x:v>14.4</x:v>
+        <x:v>13.05</x:v>
       </x:c>
       <x:c r="C109" s="150">
-        <x:v>14.65</x:v>
+        <x:v>13.05</x:v>
       </x:c>
       <x:c r="D109" s="150">
-        <x:v>12.75</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E109" s="151">
-        <x:v>13.95</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="F109" s="152">
-        <x:v>35907</x:v>
+        <x:v>18841</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:6">
@@ -10599,19 +10605,19 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="B110" s="150">
-        <x:v>11.65</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="C110" s="150">
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="D110" s="150">
+        <x:v>12.9</x:v>
+      </x:c>
+      <x:c r="E110" s="151">
         <x:v>13.05</x:v>
       </x:c>
-      <x:c r="D110" s="150">
-        <x:v>11.4</x:v>
-      </x:c>
-      <x:c r="E110" s="151">
-        <x:v>12.95</x:v>
-      </x:c>
       <x:c r="F110" s="152">
-        <x:v>15351</x:v>
+        <x:v>9310</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:6">
@@ -10619,19 +10625,19 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B111" s="150">
-        <x:v>12.5</x:v>
+        <x:v>14.4</x:v>
       </x:c>
       <x:c r="C111" s="150">
-        <x:v>12.5</x:v>
+        <x:v>14.65</x:v>
       </x:c>
       <x:c r="D111" s="150">
-        <x:v>12.5</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="E111" s="151">
-        <x:v>12.5</x:v>
+        <x:v>13.95</x:v>
       </x:c>
       <x:c r="F111" s="152">
-        <x:v>408</x:v>
+        <x:v>35907</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:6">
@@ -10639,19 +10645,19 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B112" s="150">
-        <x:v>12.1</x:v>
+        <x:v>11.65</x:v>
       </x:c>
       <x:c r="C112" s="150">
-        <x:v>12.1</x:v>
+        <x:v>13.05</x:v>
       </x:c>
       <x:c r="D112" s="150">
-        <x:v>11.25</x:v>
+        <x:v>11.4</x:v>
       </x:c>
       <x:c r="E112" s="151">
-        <x:v>12.05</x:v>
+        <x:v>12.95</x:v>
       </x:c>
       <x:c r="F112" s="152">
-        <x:v>11387</x:v>
+        <x:v>15351</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:6">
@@ -10659,19 +10665,19 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="B113" s="150">
-        <x:v>12.05</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="C113" s="150">
-        <x:v>12.9</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="D113" s="150">
-        <x:v>11.55</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E113" s="151">
-        <x:v>11.55</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="F113" s="152">
-        <x:v>20882</x:v>
+        <x:v>408</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:6">
@@ -10679,19 +10685,19 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="B114" s="150">
-        <x:v>10.85</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C114" s="150">
-        <x:v>12.35</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="D114" s="150">
-        <x:v>10.85</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="E114" s="151">
         <x:v>12.05</x:v>
       </x:c>
       <x:c r="F114" s="152">
-        <x:v>25434</x:v>
+        <x:v>11387</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:6">
@@ -10699,19 +10705,19 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B115" s="150">
-        <x:v>11.5</x:v>
+        <x:v>12.05</x:v>
       </x:c>
       <x:c r="C115" s="150">
-        <x:v>12.4</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="D115" s="150">
-        <x:v>10</x:v>
+        <x:v>11.55</x:v>
       </x:c>
       <x:c r="E115" s="151">
-        <x:v>11.25</x:v>
+        <x:v>11.55</x:v>
       </x:c>
       <x:c r="F115" s="152">
-        <x:v>54526</x:v>
+        <x:v>20882</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:6">
@@ -10719,19 +10725,19 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B116" s="150">
-        <x:v>12.3</x:v>
+        <x:v>10.85</x:v>
       </x:c>
       <x:c r="C116" s="150">
-        <x:v>12.75</x:v>
+        <x:v>12.35</x:v>
       </x:c>
       <x:c r="D116" s="150">
-        <x:v>11.1</x:v>
+        <x:v>10.85</x:v>
       </x:c>
       <x:c r="E116" s="151">
-        <x:v>11.6</x:v>
+        <x:v>12.05</x:v>
       </x:c>
       <x:c r="F116" s="152">
-        <x:v>37245</x:v>
+        <x:v>25434</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:6">
@@ -10739,19 +10745,19 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="B117" s="150">
-        <x:v>12.6</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="C117" s="150">
-        <x:v>13.1</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D117" s="150">
-        <x:v>12.15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E117" s="151">
-        <x:v>12.15</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="F117" s="152">
-        <x:v>11262</x:v>
+        <x:v>54526</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:6">
@@ -10759,19 +10765,19 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B118" s="150">
-        <x:v>14.1</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="C118" s="150">
-        <x:v>14.1</x:v>
+        <x:v>12.75</x:v>
       </x:c>
       <x:c r="D118" s="150">
-        <x:v>11.9</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="E118" s="151">
-        <x:v>12.4</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="F118" s="152">
-        <x:v>13633</x:v>
+        <x:v>37245</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:6">
@@ -10779,19 +10785,19 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B119" s="150">
-        <x:v>14.8</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C119" s="150">
-        <x:v>15</x:v>
+        <x:v>13.1</x:v>
       </x:c>
       <x:c r="D119" s="150">
-        <x:v>12.5</x:v>
+        <x:v>12.15</x:v>
       </x:c>
       <x:c r="E119" s="151">
-        <x:v>12.95</x:v>
+        <x:v>12.15</x:v>
       </x:c>
       <x:c r="F119" s="152">
-        <x:v>66082</x:v>
+        <x:v>11262</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6">
@@ -10799,19 +10805,19 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B120" s="150">
-        <x:v>16</x:v>
+        <x:v>14.1</x:v>
       </x:c>
       <x:c r="C120" s="150">
-        <x:v>16</x:v>
+        <x:v>14.1</x:v>
       </x:c>
       <x:c r="D120" s="150">
-        <x:v>13.65</x:v>
+        <x:v>11.9</x:v>
       </x:c>
       <x:c r="E120" s="151">
-        <x:v>14.3</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="F120" s="152">
-        <x:v>105762</x:v>
+        <x:v>13633</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:6">
@@ -10819,19 +10825,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B121" s="150">
-        <x:v>15.55</x:v>
+        <x:v>14.8</x:v>
       </x:c>
       <x:c r="C121" s="150">
-        <x:v>15.9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D121" s="150">
-        <x:v>14.2</x:v>
+        <x:v>12.5</x:v>
       </x:c>
       <x:c r="E121" s="151">
-        <x:v>15.3</x:v>
+        <x:v>12.95</x:v>
       </x:c>
       <x:c r="F121" s="152">
-        <x:v>69523</x:v>
+        <x:v>66082</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:6">
@@ -10839,19 +10845,19 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B122" s="150">
-        <x:v>15.15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C122" s="150">
-        <x:v>15.85</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D122" s="150">
-        <x:v>15</x:v>
+        <x:v>13.65</x:v>
       </x:c>
       <x:c r="E122" s="151">
-        <x:v>15.45</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="F122" s="152">
-        <x:v>65242</x:v>
+        <x:v>105762</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:6">
@@ -10859,19 +10865,19 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="B123" s="150">
-        <x:v>17.1</x:v>
+        <x:v>15.55</x:v>
       </x:c>
       <x:c r="C123" s="150">
-        <x:v>17.1</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="D123" s="150">
-        <x:v>14.75</x:v>
+        <x:v>14.2</x:v>
       </x:c>
       <x:c r="E123" s="151">
-        <x:v>15</x:v>
+        <x:v>15.3</x:v>
       </x:c>
       <x:c r="F123" s="152">
-        <x:v>122357</x:v>
+        <x:v>69523</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:6">
@@ -10879,18 +10885,58 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B124" s="150">
-        <x:v>16</x:v>
+        <x:v>15.15</x:v>
       </x:c>
       <x:c r="C124" s="150">
-        <x:v>18.25</x:v>
+        <x:v>15.85</x:v>
       </x:c>
       <x:c r="D124" s="150">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E124" s="151">
+        <x:v>15.45</x:v>
+      </x:c>
+      <x:c r="F124" s="152">
+        <x:v>65242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:6">
+      <x:c r="A125" s="149" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B125" s="150">
         <x:v>17.1</x:v>
       </x:c>
-      <x:c r="F124" s="152">
+      <x:c r="C125" s="150">
+        <x:v>17.1</x:v>
+      </x:c>
+      <x:c r="D125" s="150">
+        <x:v>14.75</x:v>
+      </x:c>
+      <x:c r="E125" s="151">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F125" s="152">
+        <x:v>122357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:6">
+      <x:c r="A126" s="149" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B126" s="150">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C126" s="150">
+        <x:v>18.25</x:v>
+      </x:c>
+      <x:c r="D126" s="150">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E126" s="151">
+        <x:v>17.1</x:v>
+      </x:c>
+      <x:c r="F126" s="152">
         <x:v>110928</x:v>
       </x:c>
     </x:row>
